--- a/tool/kintone-resourse-generator/doc/03_結合テスト/test-data/run-list/ok.xlsx
+++ b/tool/kintone-resourse-generator/doc/03_結合テスト/test-data/run-list/ok.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\run-list\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\doc\03_結合テスト\test-data\run-list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA573BC9-6408-4244-BBE1-34BE09C2087A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9863056-0861-4552-8D3A-349BA6290A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -450,7 +450,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -458,7 +458,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>

--- a/tool/kintone-resourse-generator/doc/03_結合テスト/test-data/run-list/ok.xlsx
+++ b/tool/kintone-resourse-generator/doc/03_結合テスト/test-data/run-list/ok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\doc\03_結合テスト\test-data\run-list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9863056-0861-4552-8D3A-349BA6290A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0AAD29-4533-4243-8272-0966CC8373BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>スペース識別名</t>
   </si>
@@ -36,15 +36,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>TestSpace</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>クラススペース</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>L01</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>kkoko</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -421,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -447,21 +443,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2">
-        <v>3</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
